--- a/plc/s7-1x00/core/adt/queue/EQueueStatus-v3.0.xlsx
+++ b/plc/s7-1x00/core/adt/queue/EQueueStatus-v3.0.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\PlcFramework\code\plc\s7-1x00\core\adt\queue\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{777B2855-36F8-4AA6-A7A4-59696353220E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89A2CF99-A43D-4015-A31B-B9B07C1FD9FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="18570" yWindow="-16365" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Constants" sheetId="1" r:id="rId1"/>
@@ -130,7 +130,7 @@
     <t>Bool</t>
   </si>
   <si>
-    <t>{"version":"v3.0","author":"cyanezf","family":"core/adt/queue"}</t>
+    <t>{"version":"v3.0","author":"cyanezf","family":"core/adt/queue","status": "current", "deprecatedBy": null, "dependencies"  : []}</t>
   </si>
 </sst>
 </file>
@@ -508,7 +508,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E11"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="48.58203125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.5" bestFit="1" customWidth="1"/>
@@ -517,7 +517,7 @@
     <col min="5" max="5" width="50.25" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -534,7 +534,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>34</v>
       </c>
@@ -551,7 +551,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -568,7 +568,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>10</v>
       </c>
@@ -585,7 +585,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>13</v>
       </c>
@@ -602,7 +602,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>16</v>
       </c>
@@ -619,7 +619,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>19</v>
       </c>
@@ -636,7 +636,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>22</v>
       </c>
@@ -653,7 +653,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>25</v>
       </c>
@@ -670,7 +670,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>28</v>
       </c>
@@ -687,7 +687,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>31</v>
       </c>
